--- a/Fujiya Instruments/Junk Guitar/Junk Guitar/xlsx/VHG.xlsx
+++ b/Fujiya Instruments/Junk Guitar/Junk Guitar/xlsx/VHG.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="2385" yWindow="3945" windowWidth="24825" windowHeight="15615" tabRatio="500" firstSheet="6" activeTab="11"/>
+    <workbookView xWindow="2385" yWindow="3945" windowWidth="24825" windowHeight="15615" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="VHG Poly (Main)" sheetId="1" r:id="rId1"/>
@@ -35,6 +35,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -57,6 +72,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,6 +115,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -107,6 +152,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -135,6 +195,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -157,6 +232,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -185,6 +275,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -207,6 +312,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -235,6 +355,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -257,6 +392,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -285,6 +435,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -310,6 +475,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
@@ -326,7 +506,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="250">
   <si>
     <t>Name</t>
   </si>
@@ -1038,12 +1218,51 @@
   <si>
     <t>Noise (Rnd) Vel 127</t>
   </si>
+  <si>
+    <t>Expression Map Name</t>
+  </si>
+  <si>
+    <t>VHG Poly (Main)</t>
+  </si>
+  <si>
+    <t>VHG Poly (Other)</t>
+  </si>
+  <si>
+    <t>VHG Mono (Main)</t>
+  </si>
+  <si>
+    <t>VHG Mono (Other)</t>
+  </si>
+  <si>
+    <t>VHG Mono (Stop)</t>
+  </si>
+  <si>
+    <t>VHG Real Chord (Stop)</t>
+  </si>
+  <si>
+    <t>VHG Simulate Chord</t>
+  </si>
+  <si>
+    <t>VHG Arpeggio</t>
+  </si>
+  <si>
+    <t>VHG Riff (Main)</t>
+  </si>
+  <si>
+    <t>VHG Riff (Chord)</t>
+  </si>
+  <si>
+    <t>VHG Riff (Other)</t>
+  </si>
+  <si>
+    <t>VHG Riff (Stop)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1103,8 +1322,15 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1157,6 +1383,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBEEF4"/>
         <bgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39994506668294322"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1219,7 +1451,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1291,6 +1523,12 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1382,13 +1620,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1687,7 +1925,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1695,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -1708,100 +1946,59 @@
     <col min="1026" max="16384" width="8.875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="19">
-        <v>120</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>12</v>
@@ -1809,12 +2006,8 @@
       <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="19">
-        <v>120</v>
-      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -1822,13 +2015,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>12</v>
@@ -1837,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G5" s="19">
         <v>120</v>
@@ -1849,13 +2042,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B6" s="19">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>12</v>
@@ -1864,7 +2057,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G6" s="19">
         <v>120</v>
@@ -1876,13 +2069,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>12</v>
@@ -1891,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G7" s="19">
         <v>120</v>
@@ -1903,13 +2096,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>12</v>
@@ -1918,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G8" s="19">
         <v>120</v>
@@ -1930,13 +2123,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>12</v>
@@ -1945,7 +2138,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G9" s="19">
         <v>120</v>
@@ -1957,13 +2150,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B10" s="19">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>12</v>
@@ -1972,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G10" s="19">
         <v>120</v>
@@ -1984,13 +2177,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B11" s="19">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>12</v>
@@ -1999,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G11" s="19">
         <v>120</v>
@@ -2011,13 +2204,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" s="19">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>12</v>
@@ -2026,7 +2219,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G12" s="19">
         <v>120</v>
@@ -2038,13 +2231,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B13" s="19">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>12</v>
@@ -2053,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G13" s="19">
         <v>120</v>
@@ -2065,13 +2258,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B14" s="19">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>12</v>
@@ -2080,7 +2273,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G14" s="19">
         <v>120</v>
@@ -2092,13 +2285,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B15" s="19">
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>12</v>
@@ -2107,7 +2300,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G15" s="19">
         <v>120</v>
@@ -2119,13 +2312,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B16" s="19">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>12</v>
@@ -2134,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G16" s="19">
         <v>120</v>
@@ -2146,13 +2339,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B17" s="19">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>12</v>
@@ -2161,7 +2354,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G17" s="19">
         <v>120</v>
@@ -2173,13 +2366,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B18" s="19">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>12</v>
@@ -2188,7 +2381,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G18" s="19">
         <v>120</v>
@@ -2199,26 +2392,54 @@
       <c r="K18" s="19"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="1"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="A19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B19" s="19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="19">
+        <v>1</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="19">
+        <v>120</v>
+      </c>
       <c r="H19" s="19"/>
       <c r="I19" s="19"/>
       <c r="J19" s="19"/>
       <c r="K19" s="19"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="1"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
+      <c r="A20" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B20" s="19">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="19">
+        <v>1</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="19">
+        <v>120</v>
+      </c>
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
       <c r="J20" s="19"/>
@@ -3641,26 +3862,55 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -3679,7 +3929,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -3688,7 +3938,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -3697,7 +3947,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3707,7 +3957,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -3720,100 +3970,59 @@
     <col min="1026" max="16384" width="8.875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="19">
-        <v>120</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>217</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>217</v>
+        <v>11</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>12</v>
@@ -3821,12 +4030,8 @@
       <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="19">
-        <v>120</v>
-      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -3834,13 +4039,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>12</v>
@@ -3849,7 +4054,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G5" s="19">
         <v>120</v>
@@ -3861,13 +4066,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B6" s="19">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>12</v>
@@ -3876,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G6" s="19">
         <v>120</v>
@@ -3888,13 +4093,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>12</v>
@@ -3903,7 +4108,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G7" s="19">
         <v>120</v>
@@ -3915,13 +4120,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>12</v>
@@ -3930,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G8" s="19">
         <v>120</v>
@@ -3942,13 +4147,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>12</v>
@@ -3957,7 +4162,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G9" s="19">
         <v>120</v>
@@ -3969,13 +4174,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B10" s="19">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>12</v>
@@ -3984,7 +4189,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G10" s="19">
         <v>120</v>
@@ -3996,13 +4201,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B11" s="19">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>12</v>
@@ -4011,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G11" s="19">
         <v>120</v>
@@ -4023,13 +4228,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B12" s="19">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>12</v>
@@ -4038,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G12" s="19">
         <v>120</v>
@@ -4050,13 +4255,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B13" s="19">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>12</v>
@@ -4065,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G13" s="19">
         <v>120</v>
@@ -4077,13 +4282,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B14" s="19">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>12</v>
@@ -4092,7 +4297,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G14" s="19">
         <v>120</v>
@@ -4104,13 +4309,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B15" s="19">
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>12</v>
@@ -4119,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G15" s="19">
         <v>120</v>
@@ -4130,26 +4335,54 @@
       <c r="K15" s="19"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="1"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
+      <c r="A16" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B16" s="19">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="19">
+        <v>1</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="19">
+        <v>120</v>
+      </c>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
       <c r="J16" s="19"/>
       <c r="K16" s="19"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="1"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
+      <c r="A17" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B17" s="19">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="19">
+        <v>1</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="19">
+        <v>120</v>
+      </c>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
       <c r="J17" s="19"/>
@@ -5611,26 +5844,55 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5648,7 +5910,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -5657,7 +5919,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -5666,7 +5928,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5676,7 +5938,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -5689,100 +5951,59 @@
     <col min="1026" max="16384" width="8.875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="19">
-        <v>120</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>12</v>
@@ -5790,12 +6011,8 @@
       <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="19">
-        <v>120</v>
-      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -5803,13 +6020,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>12</v>
@@ -5818,7 +6035,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G5" s="19">
         <v>120</v>
@@ -5829,26 +6046,54 @@
       <c r="K5" s="19"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
+      <c r="A6" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="19">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="19">
+        <v>1</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="19">
+        <v>120</v>
+      </c>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
       <c r="J6" s="19"/>
       <c r="K6" s="19"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
+      <c r="A7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="19">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="19">
+        <v>1</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="19">
+        <v>120</v>
+      </c>
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
@@ -7440,26 +7685,55 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -7477,7 +7751,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -7486,7 +7760,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -7495,7 +7769,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7505,7 +7779,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -7518,100 +7792,59 @@
     <col min="1026" max="16384" width="8.875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="19">
-        <v>15</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>172</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>172</v>
+        <v>11</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>12</v>
@@ -7619,12 +7852,8 @@
       <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="19">
-        <v>31</v>
-      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -7632,13 +7861,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>12</v>
@@ -7650,7 +7879,7 @@
         <v>46</v>
       </c>
       <c r="G5" s="19">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
@@ -7659,13 +7888,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B6" s="19">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>12</v>
@@ -7677,7 +7906,7 @@
         <v>46</v>
       </c>
       <c r="G6" s="19">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
@@ -7686,13 +7915,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>12</v>
@@ -7704,7 +7933,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="19">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
@@ -7713,13 +7942,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>12</v>
@@ -7731,7 +7960,7 @@
         <v>46</v>
       </c>
       <c r="G8" s="19">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
@@ -7740,13 +7969,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>12</v>
@@ -7758,7 +7987,7 @@
         <v>46</v>
       </c>
       <c r="G9" s="19">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="H9" s="19"/>
       <c r="I9" s="19"/>
@@ -7767,13 +7996,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B10" s="19">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>12</v>
@@ -7785,7 +8014,7 @@
         <v>46</v>
       </c>
       <c r="G10" s="19">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="H10" s="19"/>
       <c r="I10" s="19"/>
@@ -7794,13 +8023,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="B11" s="19">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>12</v>
@@ -7809,10 +8038,10 @@
         <v>1</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G11" s="19">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
@@ -7821,13 +8050,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="B12" s="19">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>12</v>
@@ -7836,10 +8065,10 @@
         <v>1</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="19">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="H12" s="19"/>
       <c r="I12" s="19"/>
@@ -7848,13 +8077,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B13" s="19">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>12</v>
@@ -7866,7 +8095,7 @@
         <v>47</v>
       </c>
       <c r="G13" s="19">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="19"/>
@@ -7875,13 +8104,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B14" s="19">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>12</v>
@@ -7893,7 +8122,7 @@
         <v>47</v>
       </c>
       <c r="G14" s="19">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H14" s="19"/>
       <c r="I14" s="19"/>
@@ -7902,13 +8131,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B15" s="19">
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>12</v>
@@ -7920,7 +8149,7 @@
         <v>47</v>
       </c>
       <c r="G15" s="19">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
@@ -7929,13 +8158,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B16" s="19">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>12</v>
@@ -7947,7 +8176,7 @@
         <v>47</v>
       </c>
       <c r="G16" s="19">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
@@ -7956,13 +8185,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B17" s="19">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>12</v>
@@ -7974,7 +8203,7 @@
         <v>47</v>
       </c>
       <c r="G17" s="19">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
@@ -7983,13 +8212,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B18" s="19">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>12</v>
@@ -8001,7 +8230,7 @@
         <v>47</v>
       </c>
       <c r="G18" s="19">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -8009,26 +8238,54 @@
       <c r="K18" s="19"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="1"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="A19" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B19" s="19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="19">
+        <v>1</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="19">
+        <v>111</v>
+      </c>
       <c r="H19" s="19"/>
       <c r="I19" s="19"/>
       <c r="J19" s="19"/>
       <c r="K19" s="19"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="1"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
+      <c r="A20" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B20" s="19">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="19">
+        <v>1</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="19">
+        <v>127</v>
+      </c>
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
       <c r="J20" s="19"/>
@@ -9451,26 +9708,55 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9488,7 +9774,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -9497,7 +9783,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -9506,7 +9792,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10976,7 +11262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -10989,102 +11275,59 @@
     <col min="1026" max="16384" width="8.875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19">
-        <v>120</v>
-      </c>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="19">
-        <v>120</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>12</v>
@@ -11092,9 +11335,7 @@
       <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>22</v>
-      </c>
+      <c r="F4" s="19"/>
       <c r="G4" s="19">
         <v>120</v>
       </c>
@@ -11105,13 +11346,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>12</v>
@@ -11120,7 +11361,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5" s="19">
         <v>120</v>
@@ -11132,13 +11373,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B6" s="19">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>12</v>
@@ -11147,10 +11388,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="G6" s="19">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
@@ -11159,13 +11400,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>12</v>
@@ -11174,10 +11415,10 @@
         <v>1</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G7" s="19">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
@@ -11185,26 +11426,54 @@
       <c r="K7" s="19"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
+      <c r="A8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="19">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="19">
+        <v>1</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="19">
+        <v>64</v>
+      </c>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
       <c r="K8" s="19"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+      <c r="A9" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="19">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="19">
+        <v>1</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="19">
+        <v>65</v>
+      </c>
       <c r="H9" s="19"/>
       <c r="I9" s="19"/>
       <c r="J9" s="19"/>
@@ -12770,26 +13039,55 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12807,7 +13105,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -12816,7 +13114,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -12825,7 +13123,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12835,7 +13133,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -12848,100 +13146,59 @@
     <col min="1026" max="16384" width="8.875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="19">
-        <v>120</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>12</v>
@@ -12949,12 +13206,8 @@
       <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="19">
-        <v>120</v>
-      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -12962,13 +13215,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>12</v>
@@ -12977,7 +13230,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G5" s="19">
         <v>120</v>
@@ -12989,13 +13242,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B6" s="19">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>12</v>
@@ -13004,7 +13257,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G6" s="19">
         <v>120</v>
@@ -13016,13 +13269,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>12</v>
@@ -13031,7 +13284,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G7" s="19">
         <v>120</v>
@@ -13043,13 +13296,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>12</v>
@@ -13058,7 +13311,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G8" s="19">
         <v>120</v>
@@ -13070,13 +13323,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>12</v>
@@ -13085,7 +13338,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G9" s="19">
         <v>120</v>
@@ -13097,13 +13350,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B10" s="19">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>12</v>
@@ -13112,7 +13365,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G10" s="19">
         <v>120</v>
@@ -13124,13 +13377,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B11" s="19">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>12</v>
@@ -13139,7 +13392,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G11" s="19">
         <v>120</v>
@@ -13151,13 +13404,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B12" s="19">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>12</v>
@@ -13166,7 +13419,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G12" s="19">
         <v>120</v>
@@ -13178,13 +13431,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B13" s="19">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>12</v>
@@ -13193,7 +13446,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G13" s="19">
         <v>120</v>
@@ -13205,13 +13458,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B14" s="19">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>12</v>
@@ -13220,7 +13473,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G14" s="19">
         <v>120</v>
@@ -13232,13 +13485,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B15" s="19">
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>12</v>
@@ -13247,7 +13500,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G15" s="19">
         <v>120</v>
@@ -13259,13 +13512,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B16" s="19">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>12</v>
@@ -13274,7 +13527,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G16" s="19">
         <v>120</v>
@@ -13286,13 +13539,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B17" s="19">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>12</v>
@@ -13301,7 +13554,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G17" s="19">
         <v>120</v>
@@ -13313,13 +13566,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="B18" s="19">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>12</v>
@@ -13328,7 +13581,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G18" s="19">
         <v>120</v>
@@ -13340,13 +13593,13 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B19" s="19">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>12</v>
@@ -13355,7 +13608,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G19" s="19">
         <v>120</v>
@@ -13367,13 +13620,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B20" s="19">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>12</v>
@@ -13382,7 +13635,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G20" s="19">
         <v>120</v>
@@ -13394,13 +13647,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B21" s="19">
         <v>1</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>12</v>
@@ -13409,7 +13662,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G21" s="19">
         <v>120</v>
@@ -13421,13 +13674,13 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B22" s="19">
         <v>1</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>12</v>
@@ -13436,7 +13689,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G22" s="19">
         <v>120</v>
@@ -13447,26 +13700,54 @@
       <c r="K22" s="19"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="1"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
+      <c r="A23" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" s="19">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="19">
+        <v>1</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="19">
+        <v>120</v>
+      </c>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
       <c r="J23" s="19"/>
       <c r="K23" s="19"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="1"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
+      <c r="A24" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="19">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="19">
+        <v>1</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="19">
+        <v>120</v>
+      </c>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
       <c r="J24" s="19"/>
@@ -14837,26 +15118,55 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -14874,7 +15184,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -14883,7 +15193,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -14892,7 +15202,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -14902,7 +15212,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -14915,100 +15225,59 @@
     <col min="1026" max="16384" width="8.875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="19">
-        <v>120</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>12</v>
@@ -15016,12 +15285,8 @@
       <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="19">
-        <v>120</v>
-      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -15029,13 +15294,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>12</v>
@@ -15044,7 +15309,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5" s="19">
         <v>120</v>
@@ -15055,26 +15320,54 @@
       <c r="K5" s="19"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
+      <c r="A6" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="19">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="19">
+        <v>1</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="19">
+        <v>120</v>
+      </c>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
       <c r="J6" s="19"/>
       <c r="K6" s="19"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
+      <c r="A7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="19">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="19">
+        <v>1</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="19">
+        <v>120</v>
+      </c>
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
@@ -16666,26 +16959,55 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -16703,7 +17025,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16712,7 +17034,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16721,7 +17043,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -16731,7 +17053,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -16744,100 +17066,59 @@
     <col min="1026" max="16384" width="8.875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="19">
-        <v>15</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>172</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>172</v>
+        <v>11</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>12</v>
@@ -16845,12 +17126,8 @@
       <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="19">
-        <v>31</v>
-      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -16858,13 +17135,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>12</v>
@@ -16876,7 +17153,7 @@
         <v>46</v>
       </c>
       <c r="G5" s="19">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
@@ -16885,13 +17162,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B6" s="19">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>12</v>
@@ -16903,7 +17180,7 @@
         <v>46</v>
       </c>
       <c r="G6" s="19">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
@@ -16912,13 +17189,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>12</v>
@@ -16930,7 +17207,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="19">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
@@ -16939,13 +17216,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>12</v>
@@ -16957,7 +17234,7 @@
         <v>46</v>
       </c>
       <c r="G8" s="19">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
@@ -16966,13 +17243,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>12</v>
@@ -16984,7 +17261,7 @@
         <v>46</v>
       </c>
       <c r="G9" s="19">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="H9" s="19"/>
       <c r="I9" s="19"/>
@@ -16993,13 +17270,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B10" s="19">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>12</v>
@@ -17011,7 +17288,7 @@
         <v>46</v>
       </c>
       <c r="G10" s="19">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="H10" s="19"/>
       <c r="I10" s="19"/>
@@ -17020,13 +17297,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B11" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>12</v>
@@ -17035,10 +17312,10 @@
         <v>1</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G11" s="19">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
@@ -17047,13 +17324,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B12" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>12</v>
@@ -17062,10 +17339,10 @@
         <v>1</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="19">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="H12" s="19"/>
       <c r="I12" s="19"/>
@@ -17074,13 +17351,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B13" s="19">
         <v>2</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>12</v>
@@ -17092,7 +17369,7 @@
         <v>47</v>
       </c>
       <c r="G13" s="19">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="19"/>
@@ -17101,13 +17378,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B14" s="19">
         <v>2</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>12</v>
@@ -17119,7 +17396,7 @@
         <v>47</v>
       </c>
       <c r="G14" s="19">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H14" s="19"/>
       <c r="I14" s="19"/>
@@ -17128,13 +17405,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B15" s="19">
         <v>2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>12</v>
@@ -17146,7 +17423,7 @@
         <v>47</v>
       </c>
       <c r="G15" s="19">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
@@ -17155,13 +17432,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B16" s="19">
         <v>2</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>12</v>
@@ -17173,7 +17450,7 @@
         <v>47</v>
       </c>
       <c r="G16" s="19">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
@@ -17182,13 +17459,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B17" s="19">
         <v>2</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>12</v>
@@ -17200,7 +17477,7 @@
         <v>47</v>
       </c>
       <c r="G17" s="19">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
@@ -17209,13 +17486,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B18" s="19">
         <v>2</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>12</v>
@@ -17227,7 +17504,7 @@
         <v>47</v>
       </c>
       <c r="G18" s="19">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -17235,26 +17512,54 @@
       <c r="K18" s="19"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="1"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="A19" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19" s="19">
+        <v>2</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="19">
+        <v>1</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="19">
+        <v>111</v>
+      </c>
       <c r="H19" s="19"/>
       <c r="I19" s="19"/>
       <c r="J19" s="19"/>
       <c r="K19" s="19"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="1"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
+      <c r="A20" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B20" s="19">
+        <v>2</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="19">
+        <v>1</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="19">
+        <v>127</v>
+      </c>
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
       <c r="J20" s="19"/>
@@ -18677,26 +18982,55 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -18714,7 +19048,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -18723,7 +19057,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -18732,7 +19066,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -18742,7 +19076,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -18755,100 +19089,59 @@
     <col min="1026" max="16384" width="8.875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="G3" s="19">
-        <v>15</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>188</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>188</v>
+        <v>11</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>12</v>
@@ -18856,12 +19149,8 @@
       <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" s="19">
-        <v>31</v>
-      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -18869,13 +19158,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>12</v>
@@ -18887,7 +19176,7 @@
         <v>98</v>
       </c>
       <c r="G5" s="19">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
@@ -18896,13 +19185,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B6" s="19">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>12</v>
@@ -18914,7 +19203,7 @@
         <v>98</v>
       </c>
       <c r="G6" s="19">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
@@ -18923,13 +19212,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>12</v>
@@ -18941,7 +19230,7 @@
         <v>98</v>
       </c>
       <c r="G7" s="19">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
@@ -18950,13 +19239,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>12</v>
@@ -18968,7 +19257,7 @@
         <v>98</v>
       </c>
       <c r="G8" s="19">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
@@ -18977,13 +19266,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>12</v>
@@ -18995,7 +19284,7 @@
         <v>98</v>
       </c>
       <c r="G9" s="19">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="H9" s="19"/>
       <c r="I9" s="19"/>
@@ -19004,13 +19293,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B10" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>12</v>
@@ -19022,7 +19311,7 @@
         <v>98</v>
       </c>
       <c r="G10" s="19">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="H10" s="19"/>
       <c r="I10" s="19"/>
@@ -19031,13 +19320,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B11" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>12</v>
@@ -19046,10 +19335,10 @@
         <v>1</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G11" s="19">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
@@ -19058,13 +19347,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B12" s="19">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>12</v>
@@ -19073,10 +19362,10 @@
         <v>1</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G12" s="19">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="H12" s="19"/>
       <c r="I12" s="19"/>
@@ -19085,13 +19374,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B13" s="19">
         <v>2</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>12</v>
@@ -19103,7 +19392,7 @@
         <v>99</v>
       </c>
       <c r="G13" s="19">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="19"/>
@@ -19112,13 +19401,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B14" s="19">
         <v>2</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>12</v>
@@ -19130,7 +19419,7 @@
         <v>99</v>
       </c>
       <c r="G14" s="19">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H14" s="19"/>
       <c r="I14" s="19"/>
@@ -19139,13 +19428,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B15" s="19">
         <v>2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>12</v>
@@ -19157,7 +19446,7 @@
         <v>99</v>
       </c>
       <c r="G15" s="19">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
@@ -19166,13 +19455,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B16" s="19">
         <v>2</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>12</v>
@@ -19184,7 +19473,7 @@
         <v>99</v>
       </c>
       <c r="G16" s="19">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
@@ -19193,13 +19482,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B17" s="19">
         <v>2</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>12</v>
@@ -19211,7 +19500,7 @@
         <v>99</v>
       </c>
       <c r="G17" s="19">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
@@ -19220,13 +19509,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B18" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>12</v>
@@ -19238,7 +19527,7 @@
         <v>99</v>
       </c>
       <c r="G18" s="19">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
@@ -19247,13 +19536,13 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B19" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>12</v>
@@ -19262,10 +19551,10 @@
         <v>1</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G19" s="19">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="H19" s="19"/>
       <c r="I19" s="19"/>
@@ -19274,13 +19563,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B20" s="19">
         <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>12</v>
@@ -19289,10 +19578,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G20" s="19">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
@@ -19301,13 +19590,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B21" s="19">
         <v>3</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>12</v>
@@ -19319,7 +19608,7 @@
         <v>100</v>
       </c>
       <c r="G21" s="19">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="H21" s="19"/>
       <c r="I21" s="19"/>
@@ -19328,13 +19617,13 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B22" s="19">
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>12</v>
@@ -19346,7 +19635,7 @@
         <v>100</v>
       </c>
       <c r="G22" s="19">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
@@ -19355,13 +19644,13 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B23" s="19">
         <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>12</v>
@@ -19373,7 +19662,7 @@
         <v>100</v>
       </c>
       <c r="G23" s="19">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
@@ -19382,13 +19671,13 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B24" s="19">
         <v>3</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D24" s="20" t="s">
         <v>12</v>
@@ -19400,7 +19689,7 @@
         <v>100</v>
       </c>
       <c r="G24" s="19">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
@@ -19409,13 +19698,13 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B25" s="19">
         <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>12</v>
@@ -19427,7 +19716,7 @@
         <v>100</v>
       </c>
       <c r="G25" s="19">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
@@ -19436,13 +19725,13 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B26" s="19">
         <v>3</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>12</v>
@@ -19454,7 +19743,7 @@
         <v>100</v>
       </c>
       <c r="G26" s="19">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
@@ -19462,26 +19751,54 @@
       <c r="K26" s="19"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="1"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
+      <c r="A27" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B27" s="19">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="19">
+        <v>1</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G27" s="19">
+        <v>111</v>
+      </c>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="1"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
+      <c r="A28" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B28" s="19">
+        <v>3</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="19">
+        <v>1</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="19">
+        <v>127</v>
+      </c>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
@@ -20800,26 +21117,55 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -20837,7 +21183,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -20846,7 +21192,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -20855,7 +21201,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -20865,7 +21211,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -20878,100 +21224,59 @@
     <col min="1026" max="16384" width="8.875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="19">
-        <v>120</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>212</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>212</v>
+        <v>11</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>12</v>
@@ -20979,12 +21284,8 @@
       <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="19">
-        <v>120</v>
-      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -20992,13 +21293,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>12</v>
@@ -21007,7 +21308,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G5" s="19">
         <v>120</v>
@@ -21019,13 +21320,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B6" s="19">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>12</v>
@@ -21034,7 +21335,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G6" s="19">
         <v>120</v>
@@ -21045,26 +21346,54 @@
       <c r="K6" s="19"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
+      <c r="A7" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B7" s="19">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="19">
+        <v>1</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="19">
+        <v>120</v>
+      </c>
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
+      <c r="A8" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="19">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="19">
+        <v>1</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="19">
+        <v>120</v>
+      </c>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
@@ -22643,26 +22972,55 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -22680,7 +23038,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -22689,7 +23047,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -22698,7 +23056,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -22708,7 +23066,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -22721,100 +23079,59 @@
     <col min="1026" max="16384" width="8.875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="19">
-        <v>120</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>215</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>215</v>
+        <v>11</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>12</v>
@@ -22822,38 +23139,62 @@
       <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="19">
-        <v>120</v>
-      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
       <c r="K4" s="19"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="1"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="A5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="19">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="19">
+        <v>1</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="19">
+        <v>120</v>
+      </c>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
       <c r="K5" s="19"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
+      <c r="A6" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="19">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="19">
+        <v>1</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="19">
+        <v>120</v>
+      </c>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
       <c r="J6" s="19"/>
@@ -24458,26 +24799,55 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -24495,7 +24865,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -24504,7 +24874,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -24513,7 +24883,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -24523,7 +24893,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -24536,100 +24906,59 @@
     <col min="1026" max="16384" width="8.875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="19">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B3" s="19">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="19">
-        <v>120</v>
-      </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>12</v>
@@ -24637,12 +24966,8 @@
       <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="19">
-        <v>120</v>
-      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -24650,13 +24975,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>12</v>
@@ -24665,7 +24990,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G5" s="19">
         <v>120</v>
@@ -24677,13 +25002,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="B6" s="19">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>12</v>
@@ -24692,7 +25017,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G6" s="19">
         <v>120</v>
@@ -24704,13 +25029,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>12</v>
@@ -24719,7 +25044,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G7" s="19">
         <v>120</v>
@@ -24731,13 +25056,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>12</v>
@@ -24746,7 +25071,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G8" s="19">
         <v>120</v>
@@ -24758,13 +25083,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>12</v>
@@ -24773,7 +25098,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G9" s="19">
         <v>120</v>
@@ -24785,13 +25110,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B10" s="19">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>12</v>
@@ -24800,7 +25125,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G10" s="19">
         <v>120</v>
@@ -24811,26 +25136,54 @@
       <c r="K10" s="19"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
+      <c r="A11" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="19">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="19">
+        <v>1</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="19">
+        <v>120</v>
+      </c>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
       <c r="K11" s="19"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="1"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
+      <c r="A12" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="19">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="19">
+        <v>1</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="19">
+        <v>120</v>
+      </c>
       <c r="H12" s="19"/>
       <c r="I12" s="19"/>
       <c r="J12" s="19"/>
@@ -26357,26 +26710,55 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
+    <row r="130" spans="1:11">
+      <c r="A130" s="1"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" s="1"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B129">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G2:G129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J2:J129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K2:K129">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -26394,7 +26776,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D129</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -26403,7 +26785,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E2:E129</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty.">
           <x14:formula1>
@@ -26412,7 +26794,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F2:F129</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Fujiya Instruments/Junk Guitar/Junk Guitar/xlsx/VHG.xlsx
+++ b/Fujiya Instruments/Junk Guitar/Junk Guitar/xlsx/VHG.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ADCEAFC-048B-4F4B-8F69-27E1D953B0EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E173163-4FD6-4AFD-84AB-F295EE9CE687}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="1005" windowWidth="25365" windowHeight="14160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1110" yWindow="1140" windowWidth="25365" windowHeight="14160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VHG Poly (Main)" sheetId="1" r:id="rId1"/>
@@ -1529,10 +1529,10 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1637,7 +1637,7 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1950,7 +1950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -1964,7 +1964,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>237</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -2032,25 +2032,25 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>250</v>
+        <v>143</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="D5" s="24" t="s">
+      <c r="C5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="20" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="19">
         <v>1</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="G5" s="19">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B6" s="19">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>12</v>
@@ -2074,7 +2074,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" s="19">
         <v>120</v>
@@ -2086,13 +2086,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>12</v>
@@ -2101,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7" s="19">
         <v>120</v>
@@ -2113,13 +2113,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>12</v>
@@ -2128,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" s="19">
         <v>120</v>
@@ -2140,13 +2140,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>12</v>
@@ -2155,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" s="19">
         <v>120</v>
@@ -2167,13 +2167,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B10" s="19">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>12</v>
@@ -2182,7 +2182,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G10" s="19">
         <v>120</v>
@@ -2194,13 +2194,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" s="19">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>12</v>
@@ -2209,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" s="19">
         <v>120</v>
@@ -2221,13 +2221,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" s="19">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>12</v>
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" s="19">
         <v>120</v>
@@ -2248,13 +2248,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B13" s="19">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>12</v>
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G13" s="19">
         <v>120</v>
@@ -2275,13 +2275,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B14" s="19">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>12</v>
@@ -2290,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G14" s="19">
         <v>120</v>
@@ -2302,13 +2302,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B15" s="19">
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>12</v>
@@ -2317,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G15" s="19">
         <v>120</v>
@@ -2329,13 +2329,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B16" s="19">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>12</v>
@@ -2344,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" s="19">
         <v>120</v>
@@ -2356,13 +2356,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B17" s="19">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>12</v>
@@ -2371,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" s="19">
         <v>120</v>
@@ -2383,13 +2383,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B18" s="19">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>12</v>
@@ -2398,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G18" s="19">
         <v>120</v>
@@ -2410,13 +2410,13 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B19" s="19">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>12</v>
@@ -2425,7 +2425,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G19" s="19">
         <v>120</v>
@@ -2437,13 +2437,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B20" s="19">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>12</v>
@@ -2452,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G20" s="19">
         <v>120</v>
@@ -2463,27 +2463,13 @@
       <c r="K20" s="19"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B21" s="19">
-        <v>1</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="19">
-        <v>1</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="19">
-        <v>120</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
       <c r="H21" s="19"/>
       <c r="I21" s="19"/>
       <c r="J21" s="19"/>
@@ -3919,42 +3905,29 @@
       <c r="J131" s="19"/>
       <c r="K131" s="19"/>
     </row>
-    <row r="132" spans="1:11">
-      <c r="A132" s="1"/>
-      <c r="B132" s="19"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="20"/>
-      <c r="E132" s="19"/>
-      <c r="F132" s="19"/>
-      <c r="G132" s="19"/>
-      <c r="H132" s="19"/>
-      <c r="I132" s="19"/>
-      <c r="J132" s="19"/>
-      <c r="K132" s="19"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:C1"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B132" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I132" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G132" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J132" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K132" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -3973,7 +3946,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D4:D132</xm:sqref>
+          <xm:sqref>D4:D131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
           <x14:formula1>
@@ -3982,7 +3955,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E4:E132</xm:sqref>
+          <xm:sqref>E4:E131</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty." xr:uid="{00000000-0002-0000-0000-000007000000}">
           <x14:formula1>
@@ -3991,7 +3964,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F4:F132</xm:sqref>
+          <xm:sqref>F4:F131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4015,7 +3988,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>237</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -5996,7 +5969,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>237</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -7837,7 +7810,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>237</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -11320,7 +11293,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>237</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -13177,7 +13150,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="39.5" style="21" customWidth="1"/>
@@ -13191,7 +13164,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>237</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -13259,25 +13232,25 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>164</v>
+        <v>250</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D5" s="20" t="s">
+      <c r="C5" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D5" s="25" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="19">
         <v>1</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="G5" s="19">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
@@ -13286,13 +13259,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="19">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>12</v>
@@ -13301,7 +13274,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" s="19">
         <v>120</v>
@@ -13313,13 +13286,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>12</v>
@@ -13328,7 +13301,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" s="19">
         <v>120</v>
@@ -13340,13 +13313,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>12</v>
@@ -13355,7 +13328,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="19">
         <v>120</v>
@@ -13367,13 +13340,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>12</v>
@@ -13382,7 +13355,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" s="19">
         <v>120</v>
@@ -13394,13 +13367,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="B10" s="19">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>12</v>
@@ -13409,7 +13382,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" s="19">
         <v>120</v>
@@ -13421,13 +13394,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B11" s="19">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>12</v>
@@ -13436,7 +13409,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" s="19">
         <v>120</v>
@@ -13448,13 +13421,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B12" s="19">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>12</v>
@@ -13463,7 +13436,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G12" s="19">
         <v>120</v>
@@ -13475,13 +13448,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" s="19">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>12</v>
@@ -13490,7 +13463,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G13" s="19">
         <v>120</v>
@@ -13502,13 +13475,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B14" s="19">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>12</v>
@@ -13517,7 +13490,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G14" s="19">
         <v>120</v>
@@ -13529,13 +13502,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B15" s="19">
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>12</v>
@@ -13544,7 +13517,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G15" s="19">
         <v>120</v>
@@ -13556,13 +13529,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B16" s="19">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>12</v>
@@ -13571,7 +13544,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" s="19">
         <v>120</v>
@@ -13583,13 +13556,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B17" s="19">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>12</v>
@@ -13598,7 +13571,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G17" s="19">
         <v>120</v>
@@ -13610,13 +13583,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B18" s="19">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>12</v>
@@ -13625,7 +13598,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="19">
         <v>120</v>
@@ -13637,13 +13610,13 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B19" s="19">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>12</v>
@@ -13652,7 +13625,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G19" s="19">
         <v>120</v>
@@ -13664,13 +13637,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="B20" s="19">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>12</v>
@@ -13679,7 +13652,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G20" s="19">
         <v>120</v>
@@ -13691,13 +13664,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21" s="19">
         <v>1</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>12</v>
@@ -13706,7 +13679,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G21" s="19">
         <v>120</v>
@@ -13718,13 +13691,13 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="B22" s="19">
         <v>1</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>12</v>
@@ -13733,7 +13706,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G22" s="19">
         <v>120</v>
@@ -13745,13 +13718,13 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B23" s="19">
         <v>1</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>12</v>
@@ -13760,7 +13733,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G23" s="19">
         <v>120</v>
@@ -13772,13 +13745,13 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B24" s="19">
         <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D24" s="20" t="s">
         <v>12</v>
@@ -13787,7 +13760,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G24" s="19">
         <v>120</v>
@@ -13798,13 +13771,27 @@
       <c r="K24" s="19"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="1"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
+      <c r="A25" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="19">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="19">
+        <v>1</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="19">
+        <v>120</v>
+      </c>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
       <c r="J25" s="19"/>
@@ -15188,29 +15175,42 @@
       <c r="J131" s="19"/>
       <c r="K131" s="19"/>
     </row>
+    <row r="132" spans="1:11">
+      <c r="A132" s="1"/>
+      <c r="B132" s="19"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="20"/>
+      <c r="E132" s="19"/>
+      <c r="F132" s="19"/>
+      <c r="G132" s="19"/>
+      <c r="H132" s="19"/>
+      <c r="I132" s="19"/>
+      <c r="J132" s="19"/>
+      <c r="K132" s="19"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:C1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B131" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B132" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I131" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I132" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G131" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty." sqref="G4:G132" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J131" xr:uid="{00000000-0002-0000-0200-000003000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use Program Change, set cell value empty." sqref="J4:J132" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K131" xr:uid="{00000000-0002-0000-0200-000004000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If cell value is empty, MSB will be set 0._x000a__x000a_By my research, Maybe Cubase will not recognize MSB." sqref="K4:K132" xr:uid="{00000000-0002-0000-0200-000004000000}">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -15228,7 +15228,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D4:D131</xm:sqref>
+          <xm:sqref>D4:D132</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000006000000}">
           <x14:formula1>
@@ -15237,7 +15237,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E4:E131</xm:sqref>
+          <xm:sqref>E4:E132</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="MIDI Note" prompt="Choose from Drop-down list or imput number directly(0-127)_x000a__x000a_If don’t use MIDI Note, set Cell value empty." xr:uid="{00000000-0002-0000-0200-000007000000}">
           <x14:formula1>
@@ -15246,7 +15246,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F4:F131</xm:sqref>
+          <xm:sqref>F4:F132</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -15270,7 +15270,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>237</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -17111,7 +17111,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>237</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -19134,7 +19134,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>237</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -21269,7 +21269,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>237</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -23124,7 +23124,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>237</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -24951,7 +24951,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>237</v>
       </c>
       <c r="B1" s="26" t="s">
